--- a/Avantis Mapping/SPARQL_supercategory.xlsx
+++ b/Avantis Mapping/SPARQL_supercategory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48A975D-0680-4BFE-ADE6-ACD64EAE416E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8645141F-F180-470E-8949-C7586C36A4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="321">
-  <si>
-    <t>Lagoon</t>
-  </si>
-  <si>
-    <t>Sensor,Gas</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="241">
   <si>
     <t>Vessel,Pressure,Surge</t>
   </si>
@@ -50,15 +44,6 @@
     <t>Burner,Waste Gas</t>
   </si>
   <si>
-    <t>Well,Reservoir</t>
-  </si>
-  <si>
-    <t>Charger,Battery</t>
-  </si>
-  <si>
-    <t>fvyuLoad Break Switch</t>
-  </si>
-  <si>
     <t>Air Handling Unit</t>
   </si>
   <si>
@@ -68,9 +53,6 @@
     <t>Silencer</t>
   </si>
   <si>
-    <t>PPE</t>
-  </si>
-  <si>
     <t>Conveyor,Screw,Shaftless</t>
   </si>
   <si>
@@ -95,9 +77,6 @@
     <t>Computer Equipment,UPS</t>
   </si>
   <si>
-    <t>Analyzer</t>
-  </si>
-  <si>
     <t>Tank,Non-Pressurized</t>
   </si>
   <si>
@@ -110,9 +89,6 @@
     <t>Roof Type,Tile</t>
   </si>
   <si>
-    <t>Switch,Level-High</t>
-  </si>
-  <si>
     <t>Lighting,General</t>
   </si>
   <si>
@@ -143,18 +119,12 @@
     <t>Regulator</t>
   </si>
   <si>
-    <t>Blower,Centrifugal</t>
-  </si>
-  <si>
     <t>Roof Type,Shingle</t>
   </si>
   <si>
     <t>Valve,Air Release</t>
   </si>
   <si>
-    <t>Fan,Centrifugal</t>
-  </si>
-  <si>
     <t>Valve,Pressure Reducing</t>
   </si>
   <si>
@@ -194,12 +164,6 @@
     <t>Pressure Sensor,Gauge</t>
   </si>
   <si>
-    <t>Switch,Vibration-Low</t>
-  </si>
-  <si>
-    <t>Weigh Scale,Axle</t>
-  </si>
-  <si>
     <t>Compressor,Portable,Trailer Mount</t>
   </si>
   <si>
@@ -239,9 +203,6 @@
     <t>Ultraviolet Disinfection,Bank</t>
   </si>
   <si>
-    <t>Switch,Vibration-High</t>
-  </si>
-  <si>
     <t>Roof Type,Slate</t>
   </si>
   <si>
@@ -257,24 +218,12 @@
     <t>Transmitter,Flow</t>
   </si>
   <si>
-    <t>Atmosphere Monitoring Device,Portable</t>
-  </si>
-  <si>
     <t>Compressor,Stationary,Screw</t>
   </si>
   <si>
-    <t>Welding Equipment,Welding Machine</t>
-  </si>
-  <si>
     <t>Motor,AC</t>
   </si>
   <si>
-    <t>Switch,Level-High-High</t>
-  </si>
-  <si>
-    <t>Lifting Device,Hoist,Electrical</t>
-  </si>
-  <si>
     <t>Roof Type,Metal,Copper</t>
   </si>
   <si>
@@ -287,9 +236,6 @@
     <t>Meter,Level,Ultrasonic</t>
   </si>
   <si>
-    <t>Switch,Speed-High</t>
-  </si>
-  <si>
     <t>Valve,Pinch</t>
   </si>
   <si>
@@ -299,30 +245,18 @@
     <t>Screen,Trommel</t>
   </si>
   <si>
-    <t>Control Panel,Fire</t>
-  </si>
-  <si>
     <t>Computer Equipment,Memory</t>
   </si>
   <si>
     <t>Vehicle,Unlicensed</t>
   </si>
   <si>
-    <t>Switch,Temperature-High</t>
-  </si>
-  <si>
-    <t>Crane,Overhead,Fixed,Paper</t>
-  </si>
-  <si>
     <t>Valve,Plug,Act.</t>
   </si>
   <si>
     <t>Valve,Gate</t>
   </si>
   <si>
-    <t>Forklift,Gas/Propane Dual Fuel</t>
-  </si>
-  <si>
     <t>Drier,Refrigerant</t>
   </si>
   <si>
@@ -344,18 +278,12 @@
     <t>Compressor,Portable</t>
   </si>
   <si>
-    <t>Switch,Level-Low-Low</t>
-  </si>
-  <si>
     <t>Actuator,Pneumatic</t>
   </si>
   <si>
     <t>Clarifier,Rectangular</t>
   </si>
   <si>
-    <t>Fan,Axial</t>
-  </si>
-  <si>
     <t>Roof Type,Metal,Galvanized</t>
   </si>
   <si>
@@ -365,15 +293,9 @@
     <t>Controller,Pressure</t>
   </si>
   <si>
-    <t>Control Panel,Security</t>
-  </si>
-  <si>
     <t>Meter,Level,Bubbler</t>
   </si>
   <si>
-    <t>Weigh Scale,Load Cell</t>
-  </si>
-  <si>
     <t>Damper/Louver,Butterfly</t>
   </si>
   <si>
@@ -398,9 +320,6 @@
     <t>Compressor,Stationary</t>
   </si>
   <si>
-    <t>Switch,Level-Low</t>
-  </si>
-  <si>
     <t>Valve,Diaphragm,Act.</t>
   </si>
   <si>
@@ -413,12 +332,6 @@
     <t>Motor,Hydraulic</t>
   </si>
   <si>
-    <t>Switch,Speed-Low</t>
-  </si>
-  <si>
-    <t>Control Panel,Instrumentation</t>
-  </si>
-  <si>
     <t>Valve,Balance</t>
   </si>
   <si>
@@ -434,45 +347,27 @@
     <t>Agitator,Air</t>
   </si>
   <si>
-    <t>Cable,Busduct</t>
-  </si>
-  <si>
     <t>Mixer,Submersible</t>
   </si>
   <si>
     <t>Valve,Thermal</t>
   </si>
   <si>
-    <t>Crane,Overhead,Fixed</t>
-  </si>
-  <si>
     <t>Battery,Wet Cell</t>
   </si>
   <si>
-    <t>Transfer Compactor</t>
-  </si>
-  <si>
     <t>Damper/Louver,Butterfly,Single Blade</t>
   </si>
   <si>
-    <t>Crane,Overhead</t>
-  </si>
-  <si>
     <t>Actuator,Electric</t>
   </si>
   <si>
     <t>Damper/Louver,Variable Vane</t>
   </si>
   <si>
-    <t>Compactor,Stationary</t>
-  </si>
-  <si>
     <t>Valve,Knife Gate,Act.</t>
   </si>
   <si>
-    <t>Control Panel,Operator</t>
-  </si>
-  <si>
     <t>Actuator,Pneumatic,Cylinder</t>
   </si>
   <si>
@@ -500,15 +395,9 @@
     <t>Air Handling Unit,Draw Thru</t>
   </si>
   <si>
-    <t>Atmosphere Monitoring Device,Portable,Oxygen/Toxic/CH4/LEL/CL/SO2</t>
-  </si>
-  <si>
     <t>Actuator,Manual</t>
   </si>
   <si>
-    <t>Weigh Scale,Strain Gauge</t>
-  </si>
-  <si>
     <t>Actuator,Hydraulic</t>
   </si>
   <si>
@@ -518,48 +407,30 @@
     <t>Actuator,Hydraulic,Cylinder</t>
   </si>
   <si>
-    <t>Generator,Electricity,Stationary</t>
-  </si>
-  <si>
     <t>Transmitter,Humidity</t>
   </si>
   <si>
     <t>H.V.A.C.,Heater,Unit</t>
   </si>
   <si>
-    <t>Forklift,Electric</t>
-  </si>
-  <si>
     <t>Compressor,Portable,Skid Mount</t>
   </si>
   <si>
     <t>Computer Equipment,CPU</t>
   </si>
   <si>
-    <t>Generator,Electricity,Portable</t>
-  </si>
-  <si>
     <t>Atmosphere Monitoring Device,Stationary,H2S/CO/CL/Toxic/SO2/NH3</t>
   </si>
   <si>
     <t>Computer Equipment,CD Rom</t>
   </si>
   <si>
-    <t>Weigh Scale,Platform</t>
-  </si>
-  <si>
-    <t>Welding Equipment,Plasma Cutting Machine</t>
-  </si>
-  <si>
     <t>Valve,Butterfly,Act.</t>
   </si>
   <si>
     <t>Compressor,Screw</t>
   </si>
   <si>
-    <t>Switch,Pressure-High</t>
-  </si>
-  <si>
     <t>Centrifuge,Dewatering</t>
   </si>
   <si>
@@ -572,9 +443,6 @@
     <t>Actuator,Manual,Chain Wheel</t>
   </si>
   <si>
-    <t>Switch,Position-High</t>
-  </si>
-  <si>
     <t>Actuator,Manual,Hand Wheel</t>
   </si>
   <si>
@@ -593,9 +461,6 @@
     <t>Server,Tower</t>
   </si>
   <si>
-    <t>Switch,Position-Low</t>
-  </si>
-  <si>
     <t>Lighting,Portable,Trailer Mount</t>
   </si>
   <si>
@@ -620,15 +485,6 @@
     <t>Motor,AC,Wound Rotor</t>
   </si>
   <si>
-    <t>Welding Equipment</t>
-  </si>
-  <si>
-    <t>Lifting Device,Hoist,Manual</t>
-  </si>
-  <si>
-    <t>Atmosphere Monitoring Device,Portable,Mercury</t>
-  </si>
-  <si>
     <t>Meter,Level,Infrared</t>
   </si>
   <si>
@@ -650,15 +506,6 @@
     <t>Valve,Anti-Siphon</t>
   </si>
   <si>
-    <t>Compactor,Stationary,Paper</t>
-  </si>
-  <si>
-    <t>Compactor,Mobile</t>
-  </si>
-  <si>
-    <t>Welding Equipment,Oxy-Acetylene Cutting Apparatus</t>
-  </si>
-  <si>
     <t>Screen,Vibrating</t>
   </si>
   <si>
@@ -671,15 +518,6 @@
     <t>Computer Equipment,Printer</t>
   </si>
   <si>
-    <t>Control Panel,HVAC</t>
-  </si>
-  <si>
-    <t>Crane,Travelling</t>
-  </si>
-  <si>
-    <t>Welding Equipment,Welding Tools</t>
-  </si>
-  <si>
     <t>Transformer,Ignition</t>
   </si>
   <si>
@@ -707,9 +545,6 @@
     <t>Analyzer,Oxygen</t>
   </si>
   <si>
-    <t>Switch,Pressure-Low</t>
-  </si>
-  <si>
     <t>Valve,Pressure Control</t>
   </si>
   <si>
@@ -737,18 +572,9 @@
     <t>Lighting,Security</t>
   </si>
   <si>
-    <t>Blower,Positive Displacement</t>
-  </si>
-  <si>
-    <t>Crane,Overhead,Travelling</t>
-  </si>
-  <si>
     <t>Battery,Dry Cell</t>
   </si>
   <si>
-    <t>Switch,Temperature-Low</t>
-  </si>
-  <si>
     <t>Transformer,Control</t>
   </si>
   <si>
@@ -779,16 +605,10 @@
     <t>Pressure Sensor,Gauge,Pressure</t>
   </si>
   <si>
-    <t>Forklift,Propane</t>
-  </si>
-  <si>
     <t>Roof Type,Standard Build Up</t>
   </si>
   <si>
     <t>Motor,DC</t>
-  </si>
-  <si>
-    <t>Cable,Teck</t>
   </si>
   <si>
     <t>Server,Rack Mounted</t>
@@ -812,12 +632,6 @@
     <t>TWONTO</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hot_work_equipment</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#compressor</t>
   </si>
   <si>
@@ -833,15 +647,6 @@
     <t>http://www.toronto.ca/TWONTO#computer</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_or_concentration_sensor_element</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
   </si>
   <si>
@@ -851,30 +656,18 @@
     <t>http://www.toronto.ca/TWONTO#valve</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#blower</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#roof</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#crane</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#pressure_vessel</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#flow_switch</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#portable_gas_detector</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#screen</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#forklift</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#waste_gas_burner</t>
   </si>
   <si>
@@ -884,9 +677,6 @@
     <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#pond</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#server_appliance</t>
   </si>
   <si>
@@ -905,39 +695,21 @@
     <t>http://www.toronto.ca/TWONTO#transformer</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#well</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#heater</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#flocculation_tank</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#generator-set</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#elevator</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#load_break_disconnect_switch</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#centrifuge</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#battery</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#vibration_sensor_element</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#large_stationary_tool</t>
   </si>
   <si>
@@ -947,12 +719,6 @@
     <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#PPE</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#screw_conveyor</t>
   </si>
   <si>
@@ -965,21 +731,9 @@
     <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#compactor</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#position_switch</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#passenger_vehicle</t>
   </si>
   <si>
@@ -992,22 +746,28 @@
     <t>http://www.toronto.ca/TWONTO#chemical_storage_tank</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#lifting_equipment_hoist</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#UPS</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#dryer</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_or_concentration_analyzer</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#storage_tank</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#incinerator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#tool</t>
+  </si>
+  <si>
+    <t>Machine Tool,Planer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#electrical_panel_or_cabinet</t>
+  </si>
+  <si>
+    <t>Control Panel,MCC</t>
   </si>
 </sst>
 </file>
@@ -1123,8 +883,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B257" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B257" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B199" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B199" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Category"/>
@@ -1134,9 +894,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1174,7 +934,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1280,7 +1040,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1422,7 +1182,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1430,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B199"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -1439,2055 +1199,1591 @@
   <sheetData>
     <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>253</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>254</v>
+        <v>194</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>255</v>
+        <v>195</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>259</v>
+        <v>199</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>263</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>266</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s">
-        <v>218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>267</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s">
-        <v>250</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>268</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="B26" t="s">
-        <v>212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s">
-        <v>213</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s">
-        <v>245</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>272</v>
+        <v>210</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="B31" t="s">
-        <v>196</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>212</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>274</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
-        <v>207</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>247</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>277</v>
+        <v>203</v>
       </c>
       <c r="B39" t="s">
-        <v>252</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>280</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>281</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>282</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>283</v>
+        <v>197</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>262</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>281</v>
+        <v>196</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>284</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="B51" t="s">
-        <v>179</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>270</v>
+        <v>202</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="B55" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>285</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>286</v>
+        <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>287</v>
+        <v>200</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>288</v>
+        <v>202</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>289</v>
+        <v>197</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>259</v>
+        <v>214</v>
       </c>
       <c r="B63" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="B64" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="B65" t="s">
-        <v>186</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>273</v>
+        <v>222</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="B67" t="s">
-        <v>160</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>291</v>
+        <v>202</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>265</v>
+        <v>200</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>292</v>
+        <v>224</v>
       </c>
       <c r="B70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>293</v>
+        <v>216</v>
       </c>
       <c r="B72" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>267</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>263</v>
+        <v>202</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>294</v>
+        <v>210</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="B80" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="B83" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>259</v>
+        <v>214</v>
       </c>
       <c r="B85" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
       <c r="B86" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="B87" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>284</v>
+        <v>211</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="B89" t="s">
-        <v>238</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>297</v>
+        <v>222</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>298</v>
+        <v>214</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="B93" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="B94" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>273</v>
+        <v>202</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="B97" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>302</v>
+        <v>200</v>
       </c>
       <c r="B98" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>303</v>
+        <v>199</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="B100" t="s">
-        <v>233</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>287</v>
+        <v>203</v>
       </c>
       <c r="B101" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="B102" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>258</v>
+        <v>203</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="B104" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="B105" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>296</v>
+        <v>201</v>
       </c>
       <c r="B107" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>298</v>
+        <v>216</v>
       </c>
       <c r="B108" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>280</v>
+        <v>195</v>
       </c>
       <c r="B109" t="s">
-        <v>184</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>304</v>
+        <v>208</v>
       </c>
       <c r="B110" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>294</v>
+        <v>199</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>267</v>
+        <v>212</v>
       </c>
       <c r="B113" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>305</v>
+        <v>209</v>
       </c>
       <c r="B114" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B115" t="s">
-        <v>225</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>306</v>
+        <v>195</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>125</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>303</v>
+        <v>213</v>
       </c>
       <c r="B117" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="B118" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="B119" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>282</v>
+        <v>202</v>
       </c>
       <c r="B120" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>306</v>
+        <v>198</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="B122" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="B123" t="s">
-        <v>103</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>307</v>
+        <v>202</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>298</v>
+        <v>222</v>
       </c>
       <c r="B125" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="B126" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="B127" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="B128" t="s">
-        <v>215</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>267</v>
+        <v>197</v>
       </c>
       <c r="B129" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="B130" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="B132" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>185</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>303</v>
+        <v>232</v>
       </c>
       <c r="B134" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="B135" t="s">
-        <v>210</v>
+        <v>94</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
       <c r="B136" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>308</v>
+        <v>202</v>
       </c>
       <c r="B137" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B138" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="B139" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B140" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="B141" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>305</v>
+        <v>202</v>
       </c>
       <c r="B142" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="B143" t="s">
-        <v>224</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="B144" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="B145" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>309</v>
+        <v>229</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="B147" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="B148" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="B149" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>277</v>
+        <v>202</v>
       </c>
       <c r="B150" t="s">
-        <v>66</v>
+        <v>186</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>310</v>
+        <v>203</v>
       </c>
       <c r="B151" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>311</v>
+        <v>202</v>
       </c>
       <c r="B152" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="B153" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>282</v>
+        <v>233</v>
       </c>
       <c r="B154" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>278</v>
+        <v>195</v>
       </c>
       <c r="B155" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="B156" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="B157" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>283</v>
+        <v>222</v>
       </c>
       <c r="B158" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>281</v>
+        <v>211</v>
       </c>
       <c r="B159" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
       <c r="B160" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B161" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="B162" t="s">
-        <v>249</v>
+        <v>119</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>312</v>
+        <v>220</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="B164" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
       <c r="B165" t="s">
-        <v>226</v>
+        <v>61</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="B166" t="s">
-        <v>216</v>
+        <v>85</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>313</v>
+        <v>217</v>
       </c>
       <c r="B167" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>269</v>
+        <v>201</v>
       </c>
       <c r="B168" t="s">
-        <v>248</v>
+        <v>151</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>289</v>
+        <v>202</v>
       </c>
       <c r="B169" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>259</v>
+        <v>216</v>
       </c>
       <c r="B170" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="B171" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="B172" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="B173" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="B174" t="s">
-        <v>240</v>
+        <v>181</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="B175" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>314</v>
+        <v>236</v>
       </c>
       <c r="B176" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>315</v>
+        <v>202</v>
       </c>
       <c r="B177" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>267</v>
+        <v>197</v>
       </c>
       <c r="B178" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="B179" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>269</v>
+        <v>202</v>
       </c>
       <c r="B180" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="B181" t="s">
-        <v>194</v>
+        <v>109</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="B182" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="B183" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="B184" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>263</v>
+        <v>202</v>
       </c>
       <c r="B185" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>284</v>
+        <v>199</v>
       </c>
       <c r="B186" t="s">
-        <v>230</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="B187" t="s">
-        <v>241</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>308</v>
+        <v>218</v>
       </c>
       <c r="B188" t="s">
-        <v>236</v>
+        <v>92</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="B189" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="B190" t="s">
-        <v>232</v>
+        <v>26</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>301</v>
+        <v>199</v>
       </c>
       <c r="B191" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="B192" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
       <c r="B194" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B195" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="B196" t="s">
-        <v>176</v>
+        <v>64</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="B197" t="s">
-        <v>244</v>
+        <v>91</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>309</v>
+        <v>237</v>
       </c>
       <c r="B198" t="s">
-        <v>173</v>
+        <v>238</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B199" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>310</v>
-      </c>
-      <c r="B200" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>267</v>
-      </c>
-      <c r="B201" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>265</v>
-      </c>
-      <c r="B202" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>316</v>
-      </c>
-      <c r="B203" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>294</v>
-      </c>
-      <c r="B204" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>257</v>
-      </c>
-      <c r="B205" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>285</v>
-      </c>
-      <c r="B206" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>281</v>
-      </c>
-      <c r="B207" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>298</v>
-      </c>
-      <c r="B208" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>281</v>
-      </c>
-      <c r="B209" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>281</v>
-      </c>
-      <c r="B210" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>317</v>
-      </c>
-      <c r="B211" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>281</v>
-      </c>
-      <c r="B212" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>318</v>
-      </c>
-      <c r="B213" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>295</v>
-      </c>
-      <c r="B214" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>267</v>
-      </c>
-      <c r="B215" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>270</v>
-      </c>
-      <c r="B216" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>260</v>
-      </c>
-      <c r="B217" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>303</v>
-      </c>
-      <c r="B218" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>289</v>
-      </c>
-      <c r="B219" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>266</v>
-      </c>
-      <c r="B220" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>267</v>
-      </c>
-      <c r="B221" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>287</v>
-      </c>
-      <c r="B222" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>287</v>
-      </c>
-      <c r="B223" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>259</v>
-      </c>
-      <c r="B224" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>281</v>
-      </c>
-      <c r="B225" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>285</v>
-      </c>
-      <c r="B226" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>319</v>
-      </c>
-      <c r="B227" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>306</v>
-      </c>
-      <c r="B228" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>320</v>
-      </c>
-      <c r="B229" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>262</v>
-      </c>
-      <c r="B230" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>267</v>
-      </c>
-      <c r="B231" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>259</v>
-      </c>
-      <c r="B232" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>262</v>
-      </c>
-      <c r="B233" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>256</v>
-      </c>
-      <c r="B234" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>267</v>
-      </c>
-      <c r="B235" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>267</v>
-      </c>
-      <c r="B236" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>267</v>
-      </c>
-      <c r="B237" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>306</v>
-      </c>
-      <c r="B238" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>267</v>
-      </c>
-      <c r="B239" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>283</v>
-      </c>
-      <c r="B240" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>260</v>
-      </c>
-      <c r="B241" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>267</v>
-      </c>
-      <c r="B242" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>261</v>
-      </c>
-      <c r="B243" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>269</v>
-      </c>
-      <c r="B244" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>263</v>
-      </c>
-      <c r="B245" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>291</v>
-      </c>
-      <c r="B246" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>293</v>
-      </c>
-      <c r="B247" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>294</v>
-      </c>
-      <c r="B248" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>267</v>
-      </c>
-      <c r="B249" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>261</v>
-      </c>
-      <c r="B250" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>285</v>
-      </c>
-      <c r="B251" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>266</v>
-      </c>
-      <c r="B252" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>267</v>
-      </c>
-      <c r="B253" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>315</v>
-      </c>
-      <c r="B254" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>317</v>
-      </c>
-      <c r="B255" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>272</v>
-      </c>
-      <c r="B256" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>285</v>
-      </c>
-      <c r="B257" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supercategory.xlsx
+++ b/Avantis Mapping/SPARQL_supercategory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8645141F-F180-470E-8949-C7586C36A4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A1A06B-F51E-4642-93B1-F8368AB19BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="272">
   <si>
     <t>Vessel,Pressure,Surge</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Machine Tool,Saw</t>
-  </si>
-  <si>
-    <t>Silencer</t>
   </si>
   <si>
     <t>Conveyor,Screw,Shaftless</t>
@@ -695,9 +692,6 @@
     <t>http://www.toronto.ca/TWONTO#transformer</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#heater</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#flocculation_tank</t>
   </si>
   <si>
@@ -716,9 +710,6 @@
     <t>http://www.toronto.ca/TWONTO#PLC</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#screw_conveyor</t>
   </si>
   <si>
@@ -768,6 +759,108 @@
   </si>
   <si>
     <t>Control Panel,MCC</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#hot_work_equipment</t>
+  </si>
+  <si>
+    <t>Welding Equipment,Oxy-Acetylene Cutting Apparatus</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#blower</t>
+  </si>
+  <si>
+    <t>Fan,Centrifugal</t>
+  </si>
+  <si>
+    <t>Welding Equipment,Welding Tools</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#forklift</t>
+  </si>
+  <si>
+    <t>Forklift,Propane</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
+  </si>
+  <si>
+    <t>Charger,Battery</t>
+  </si>
+  <si>
+    <t>Forklift,Gas/Propane Dual Fuel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fuel_burning_heater</t>
+  </si>
+  <si>
+    <t>Welding Equipment,Welding Machine</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
+  </si>
+  <si>
+    <t>Weigh Scale,Strain Gauge</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#generator</t>
+  </si>
+  <si>
+    <t>Generator,Electricity,Stationary</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#PPE</t>
+  </si>
+  <si>
+    <t>PPE</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
+  </si>
+  <si>
+    <t>Switch,Speed-Low</t>
+  </si>
+  <si>
+    <t>Blower,Positive Displacement</t>
+  </si>
+  <si>
+    <t>Blower,Centrifugal</t>
+  </si>
+  <si>
+    <t>Weigh Scale,Load Cell</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#hoist</t>
+  </si>
+  <si>
+    <t>Lifting Device,Hoist,Electrical</t>
+  </si>
+  <si>
+    <t>Fan,Axial</t>
+  </si>
+  <si>
+    <t>Generator,Electricity,Portable</t>
+  </si>
+  <si>
+    <t>Forklift,Electric</t>
+  </si>
+  <si>
+    <t>Welding Equipment</t>
+  </si>
+  <si>
+    <t>Lifting Device,Hoist,Manual</t>
+  </si>
+  <si>
+    <t>Switch,Speed-High</t>
+  </si>
+  <si>
+    <t>Weigh Scale,Platform</t>
+  </si>
+  <si>
+    <t>Welding Equipment,Plasma Cutting Machine</t>
+  </si>
+  <si>
+    <t>Weigh Scale,Axle</t>
   </si>
 </sst>
 </file>
@@ -883,8 +976,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B199" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B199" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B222" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B222" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Category"/>
@@ -1190,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B199"/>
+  <dimension ref="A1:B222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -1199,39 +1292,39 @@
   <sheetData>
     <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1239,807 +1332,807 @@
         <v>196</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="B19" t="s">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B32" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>251</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B64" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="B65" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B68" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="B70" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B73" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="B75" t="s">
-        <v>154</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>210</v>
+        <v>256</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="B79" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>258</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B83" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B84" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B86" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B89" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="B91" t="s">
-        <v>108</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="B93" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="B96" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="B97" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B99" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="B100" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="B102" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>198</v>
+        <v>261</v>
       </c>
       <c r="B104" t="s">
-        <v>97</v>
+        <v>262</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B105" t="s">
-        <v>176</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B106" t="s">
-        <v>169</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -2047,455 +2140,455 @@
         <v>201</v>
       </c>
       <c r="B107" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B108" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B109" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B110" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="B111" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B112" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B113" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B118" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B119" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="B120" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B121" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B122" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="B123" t="s">
-        <v>173</v>
+        <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B124" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="B127" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B128" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B129" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B130" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B132" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B133" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="B134" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B135" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B136" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B137" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="B138" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B139" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="B140" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B141" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B142" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B143" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="B144" t="s">
-        <v>177</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B145" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B147" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B148" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B149" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="B150" t="s">
-        <v>186</v>
+        <v>265</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B151" t="s">
-        <v>27</v>
+        <v>181</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B152" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="B153" t="s">
-        <v>172</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B155" t="s">
-        <v>130</v>
+        <v>183</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B156" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="B157" t="s">
-        <v>122</v>
+        <v>266</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="B158" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B159" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="B160" t="s">
-        <v>120</v>
+        <v>267</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="B161" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B162" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="B163" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -2503,287 +2596,471 @@
         <v>202</v>
       </c>
       <c r="B164" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B165" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="B166" t="s">
-        <v>85</v>
+        <v>268</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B167" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="B168" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B169" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="B170" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B171" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B172" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B173" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B174" t="s">
-        <v>181</v>
+        <v>99</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="B175" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B176" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="B177" t="s">
-        <v>115</v>
+        <v>269</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B178" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B179" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B180" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B181" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B183" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B184" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B185" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B186" t="s">
-        <v>38</v>
+        <v>177</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B187" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="B188" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B189" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B190" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B191" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B192" t="s">
-        <v>179</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B193" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B194" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="B195" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="B196" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="B197" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B198" t="s">
-        <v>238</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B199" t="s">
-        <v>240</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>201</v>
+      </c>
+      <c r="B200" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>196</v>
+      </c>
+      <c r="B201" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>238</v>
+      </c>
+      <c r="B202" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>201</v>
+      </c>
+      <c r="B203" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>201</v>
+      </c>
+      <c r="B204" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>201</v>
+      </c>
+      <c r="B205" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>201</v>
+      </c>
+      <c r="B206" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>212</v>
+      </c>
+      <c r="B207" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>197</v>
+      </c>
+      <c r="B208" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>201</v>
+      </c>
+      <c r="B209" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>198</v>
+      </c>
+      <c r="B210" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>202</v>
+      </c>
+      <c r="B211" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>216</v>
+      </c>
+      <c r="B212" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>217</v>
+      </c>
+      <c r="B213" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>250</v>
+      </c>
+      <c r="B214" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>201</v>
+      </c>
+      <c r="B215" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>198</v>
+      </c>
+      <c r="B216" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>214</v>
+      </c>
+      <c r="B217" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>200</v>
+      </c>
+      <c r="B218" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>201</v>
+      </c>
+      <c r="B219" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>231</v>
+      </c>
+      <c r="B220" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>204</v>
+      </c>
+      <c r="B221" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>214</v>
+      </c>
+      <c r="B222" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supercategory.xlsx
+++ b/Avantis Mapping/SPARQL_supercategory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA322EB2-200F-4B53-A4A2-723CCBB70C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44039686-1D5A-4AFC-B78E-8B922B2F1C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="325">
   <si>
     <t>Vessel,Pressure,Surge</t>
   </si>
@@ -617,159 +617,18 @@
     <t>TWONTO</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#compressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#computer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#valve</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#roof</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_vessel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#screen</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#waste_gas_burner</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#actuator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#clarifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_damper</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transformer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flocculation_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#elevator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#centrifuge</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#battery</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#PLC</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#screw_conveyor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#passenger_vehicle</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#strainer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#conveyor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_storage_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UPS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dryer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#incinerator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#tool</t>
-  </si>
-  <si>
-    <t>Machine Tool,Planer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#electrical_panel_or_cabinet</t>
-  </si>
-  <si>
-    <t>Control Panel,MCC</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hot_work_equipment</t>
-  </si>
-  <si>
     <t>Welding Equipment,Oxy-Acetylene Cutting Apparatus</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#blower</t>
-  </si>
-  <si>
     <t>Fan,Centrifugal</t>
   </si>
   <si>
     <t>Welding Equipment,Welding Tools</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#forklift</t>
-  </si>
-  <si>
     <t>Forklift,Propane</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
-  </si>
-  <si>
     <t>Charger,Battery</t>
   </si>
   <si>
@@ -779,27 +638,15 @@
     <t>Welding Equipment,Welding Machine</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
-  </si>
-  <si>
     <t>Weigh Scale,Strain Gauge</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#generator</t>
-  </si>
-  <si>
     <t>Generator,Electricity,Stationary</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#PPE</t>
-  </si>
-  <si>
     <t>PPE</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#speed_switch</t>
-  </si>
-  <si>
     <t>Switch,Speed-Low</t>
   </si>
   <si>
@@ -812,9 +659,6 @@
     <t>Weigh Scale,Load Cell</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#hoist</t>
-  </si>
-  <si>
     <t>Lifting Device,Hoist,Electrical</t>
   </si>
   <si>
@@ -845,54 +689,33 @@
     <t>Weigh Scale,Axle</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
-  </si>
-  <si>
     <t>Control Panel,Security</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
-  </si>
-  <si>
     <t>Control Panel, Electrical</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#portable_gas_detector</t>
-  </si>
-  <si>
     <t>Atmosphere Monitoring Device,Portable,Mercury</t>
   </si>
   <si>
     <t>Control Panel,Instrumentation</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#heater</t>
-  </si>
-  <si>
     <t>Atmosphere Monitoring Device,Portable</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#stationary_tool</t>
-  </si>
-  <si>
     <t>Atmosphere Monitoring Device,Portable,Oxygen/Toxic/CH4/LEL/CL/SO2</t>
   </si>
   <si>
     <t>Control Panel,Operator</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_or_concentration_analyzer</t>
-  </si>
-  <si>
     <t>Analyzer</t>
   </si>
   <si>
     <t>Control Panel, Power Distribution Panel</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
-  </si>
-  <si>
     <t>Switchgear</t>
   </si>
   <si>
@@ -900,6 +723,291 @@
   </si>
   <si>
     <t>Control Panel,Fire</t>
+  </si>
+  <si>
+    <t>fixed gas detector</t>
+  </si>
+  <si>
+    <t>transformer</t>
+  </si>
+  <si>
+    <t>actuator</t>
+  </si>
+  <si>
+    <t>valve</t>
+  </si>
+  <si>
+    <t>instrument transmitter</t>
+  </si>
+  <si>
+    <t>mixer or agitator</t>
+  </si>
+  <si>
+    <t>motor</t>
+  </si>
+  <si>
+    <t>hoist</t>
+  </si>
+  <si>
+    <t>compressor</t>
+  </si>
+  <si>
+    <t>well</t>
+  </si>
+  <si>
+    <t>Well,Reservoir</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>dryer</t>
+  </si>
+  <si>
+    <t>lighting unit</t>
+  </si>
+  <si>
+    <t>crane</t>
+  </si>
+  <si>
+    <t>Crane,Overhead,Fixed</t>
+  </si>
+  <si>
+    <t>battery charger</t>
+  </si>
+  <si>
+    <t>instrument gauge or display</t>
+  </si>
+  <si>
+    <t>Crane,Overhead</t>
+  </si>
+  <si>
+    <t>hot work equipment</t>
+  </si>
+  <si>
+    <t>temperature switch</t>
+  </si>
+  <si>
+    <t>Switch,Temperature-Low</t>
+  </si>
+  <si>
+    <t>clarifier</t>
+  </si>
+  <si>
+    <t>grinder or comminutor</t>
+  </si>
+  <si>
+    <t>passenger vehicle</t>
+  </si>
+  <si>
+    <t>roof</t>
+  </si>
+  <si>
+    <t>UV disinfection assembly</t>
+  </si>
+  <si>
+    <t>PLC</t>
+  </si>
+  <si>
+    <t>air handler unit</t>
+  </si>
+  <si>
+    <t>stationary tool</t>
+  </si>
+  <si>
+    <t>forklift</t>
+  </si>
+  <si>
+    <t>chemical or concentration sensor element</t>
+  </si>
+  <si>
+    <t>Sensor,Gas</t>
+  </si>
+  <si>
+    <t>heater</t>
+  </si>
+  <si>
+    <t>Crane,Overhead,Travelling</t>
+  </si>
+  <si>
+    <t>generator</t>
+  </si>
+  <si>
+    <t>speed switch</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>chemical storage tank</t>
+  </si>
+  <si>
+    <t>server appliance</t>
+  </si>
+  <si>
+    <t>process control panel</t>
+  </si>
+  <si>
+    <t>blower</t>
+  </si>
+  <si>
+    <t>position switch</t>
+  </si>
+  <si>
+    <t>Switch,Position-High</t>
+  </si>
+  <si>
+    <t>incinerator</t>
+  </si>
+  <si>
+    <t>level transmitter</t>
+  </si>
+  <si>
+    <t>Crane,Travelling</t>
+  </si>
+  <si>
+    <t>cable segment</t>
+  </si>
+  <si>
+    <t>Cable,Busduct</t>
+  </si>
+  <si>
+    <t>air damper</t>
+  </si>
+  <si>
+    <t>pressure vessel</t>
+  </si>
+  <si>
+    <t>centrifuge</t>
+  </si>
+  <si>
+    <t>flow switch</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>flocculation tank</t>
+  </si>
+  <si>
+    <t>screen</t>
+  </si>
+  <si>
+    <t>portable gas detector</t>
+  </si>
+  <si>
+    <t>Switch,Position-Low</t>
+  </si>
+  <si>
+    <t>pressure switch</t>
+  </si>
+  <si>
+    <t>Switch,Pressure-Low</t>
+  </si>
+  <si>
+    <t>load break disconnect switch</t>
+  </si>
+  <si>
+    <t>fvyuLoad Break Switch</t>
+  </si>
+  <si>
+    <t>MV electrical cabinet</t>
+  </si>
+  <si>
+    <t>Switch,Pressure-High</t>
+  </si>
+  <si>
+    <t>level switch</t>
+  </si>
+  <si>
+    <t>Switch,Level-Low</t>
+  </si>
+  <si>
+    <t>elevator</t>
+  </si>
+  <si>
+    <t>strainer</t>
+  </si>
+  <si>
+    <t>Switch,Level-Low-Low</t>
+  </si>
+  <si>
+    <t>Switch,Temperature-High</t>
+  </si>
+  <si>
+    <t>compactor</t>
+  </si>
+  <si>
+    <t>Compactor,Mobile</t>
+  </si>
+  <si>
+    <t>Compactor,Stationary,Paper</t>
+  </si>
+  <si>
+    <t>weight scale</t>
+  </si>
+  <si>
+    <t>LV electrical panel</t>
+  </si>
+  <si>
+    <t>pressure transmitter</t>
+  </si>
+  <si>
+    <t>Switch,Level-High-High</t>
+  </si>
+  <si>
+    <t>storage tank</t>
+  </si>
+  <si>
+    <t>vibration sensor element</t>
+  </si>
+  <si>
+    <t>Switch,Vibration-High</t>
+  </si>
+  <si>
+    <t>pond</t>
+  </si>
+  <si>
+    <t>Lagoon</t>
+  </si>
+  <si>
+    <t>waste gas burner</t>
+  </si>
+  <si>
+    <t>Switch,Vibration-Low</t>
+  </si>
+  <si>
+    <t>Transfer Compactor</t>
+  </si>
+  <si>
+    <t>Compactor,Stationary</t>
+  </si>
+  <si>
+    <t>Cable,Teck</t>
+  </si>
+  <si>
+    <t>screw conveyor</t>
+  </si>
+  <si>
+    <t>air scrubber</t>
+  </si>
+  <si>
+    <t>Crane,Overhead,Fixed,Paper</t>
+  </si>
+  <si>
+    <t>Switch,Level-High</t>
+  </si>
+  <si>
+    <t>conveyor</t>
+  </si>
+  <si>
+    <t>chemical or concentration analyzer</t>
+  </si>
+  <si>
+    <t>air duct segment</t>
+  </si>
+  <si>
+    <t>Silencer</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -907,9 +1015,10 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT ?TWONTO (STR(?object) as ?Avantis)
+SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis) 
 WHERE { 
     ?TWONTO tw:is_superclass_of_Avantis_category ?object .
+    ?TWONTO rdfs:label ?TWONTO_Label .
     FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
   </si>
@@ -1027,8 +1136,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B234" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B234" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}" name="Table1" displayName="Table1" ref="A2:B260" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B260" xr:uid="{95B7462F-2E77-4297-9361-348E17AE61B7}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F929C49D-2775-4718-8C6D-B5829C8CADDE}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{69FF631B-786D-4A8E-A604-FCCAC8BACC05}" name="Super_Category"/>
@@ -1334,16 +1443,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B234"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="203" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1356,634 +1465,634 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>237</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>271</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s">
-        <v>240</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s">
-        <v>0</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>245</v>
+      </c>
+      <c r="B25" t="s">
         <v>197</v>
-      </c>
-      <c r="B25" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s">
-        <v>274</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s">
-        <v>242</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s">
-        <v>191</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="B37" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="B39" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B42" t="s">
-        <v>275</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="B48" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="B53" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B55" t="s">
-        <v>245</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="B59" t="s">
-        <v>277</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="B65" t="s">
-        <v>42</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B66" t="s">
-        <v>246</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="B67" t="s">
-        <v>248</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="B69" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="B70" t="s">
-        <v>2</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="B71" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="B76" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B77" t="s">
-        <v>3</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="B78" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B80" t="s">
-        <v>149</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B81" t="s">
-        <v>252</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -1991,1223 +2100,1431 @@
         <v>273</v>
       </c>
       <c r="B82" t="s">
-        <v>279</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
-        <v>254</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="B84" t="s">
-        <v>39</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>195</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B86" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="B88" t="s">
-        <v>123</v>
+        <v>275</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="B90" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="B91" t="s">
-        <v>280</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="B92" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>200</v>
+        <v>279</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>208</v>
+        <v>262</v>
       </c>
       <c r="B95" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B97" t="s">
-        <v>256</v>
+        <v>169</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="B98" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="B99" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B100" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>209</v>
+        <v>282</v>
       </c>
       <c r="B101" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B102" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="B103" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="B105" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="B106" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="B107" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B109" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="B110" t="s">
-        <v>259</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>212</v>
+        <v>284</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="B113" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="B114" t="s">
-        <v>166</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B115" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="B116" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="B117" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>198</v>
+        <v>271</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>286</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>197</v>
+        <v>287</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>217</v>
+        <v>289</v>
       </c>
       <c r="B120" t="s">
-        <v>7</v>
+        <v>290</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B121" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="B123" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="B124" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="B125" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="B126" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B127" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="B128" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B129" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="B130" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="B131" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="B132" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="B133" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="B135" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>210</v>
+        <v>293</v>
       </c>
       <c r="B136" t="s">
-        <v>49</v>
+        <v>294</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="B137" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="B138" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="B139" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>211</v>
+        <v>259</v>
       </c>
       <c r="B140" t="s">
-        <v>115</v>
+        <v>196</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
       <c r="B141" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="B142" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B143" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B144" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="B145" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>196</v>
+        <v>296</v>
       </c>
       <c r="B146" t="s">
-        <v>189</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B147" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="B148" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="B149" t="s">
-        <v>161</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="B151" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>214</v>
+        <v>293</v>
       </c>
       <c r="B152" t="s">
-        <v>20</v>
+        <v>297</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="B153" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="B154" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>195</v>
+        <v>270</v>
       </c>
       <c r="B155" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B156" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>200</v>
+        <v>299</v>
       </c>
       <c r="B157" t="s">
-        <v>181</v>
+        <v>300</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="B158" t="s">
-        <v>184</v>
+        <v>123</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="B159" t="s">
-        <v>10</v>
+        <v>301</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="B160" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>201</v>
+        <v>257</v>
       </c>
       <c r="B161" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="B162" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="B163" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="B164" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="B165" t="s">
-        <v>41</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B166" t="s">
-        <v>264</v>
+        <v>135</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="B167" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
       <c r="B168" t="s">
-        <v>174</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="B169" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="B170" t="s">
-        <v>22</v>
+        <v>188</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="B171" t="s">
-        <v>176</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B172" t="s">
-        <v>265</v>
+        <v>104</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="B173" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
       <c r="B174" t="s">
-        <v>145</v>
+        <v>218</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="B175" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="B176" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="B177" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B178" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="B179" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B180" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="B181" t="s">
-        <v>171</v>
+        <v>64</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B182" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="B183" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="B184" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="B185" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="B186" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="B187" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="B188" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="B189" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B190" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>209</v>
+        <v>254</v>
       </c>
       <c r="B191" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="B192" t="s">
-        <v>282</v>
+        <v>176</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="B193" t="s">
-        <v>283</v>
+        <v>82</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B194" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="B195" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="B196" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="B197" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="B198" t="s">
-        <v>33</v>
+        <v>228</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B199" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>200</v>
+        <v>307</v>
       </c>
       <c r="B200" t="s">
-        <v>21</v>
+        <v>308</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="B201" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B202" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>195</v>
+        <v>309</v>
       </c>
       <c r="B203" t="s">
-        <v>167</v>
+        <v>310</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="B204" t="s">
-        <v>285</v>
+        <v>41</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="B205" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="B206" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B207" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B209" t="s">
-        <v>286</v>
+        <v>107</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="B210" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>195</v>
+        <v>270</v>
       </c>
       <c r="B211" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B212" t="s">
-        <v>287</v>
+        <v>222</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="B213" t="s">
-        <v>267</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="B214" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="B215" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>200</v>
+        <v>307</v>
       </c>
       <c r="B216" t="s">
-        <v>108</v>
+        <v>312</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>200</v>
+        <v>299</v>
       </c>
       <c r="B217" t="s">
-        <v>27</v>
+        <v>313</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="B218" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="B219" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B220" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>197</v>
+        <v>299</v>
       </c>
       <c r="B221" t="s">
-        <v>37</v>
+        <v>314</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>201</v>
+        <v>276</v>
       </c>
       <c r="B222" t="s">
-        <v>164</v>
+        <v>315</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="B223" t="s">
-        <v>91</v>
+        <v>214</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>216</v>
+        <v>302</v>
       </c>
       <c r="B224" t="s">
-        <v>17</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B225" t="s">
-        <v>268</v>
+        <v>37</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="B226" t="s">
-        <v>25</v>
+        <v>191</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>197</v>
+        <v>316</v>
       </c>
       <c r="B227" t="s">
-        <v>131</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>213</v>
+        <v>317</v>
       </c>
       <c r="B228" t="s">
-        <v>178</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B229" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>200</v>
+        <v>295</v>
       </c>
       <c r="B230" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="B232" t="s">
-        <v>63</v>
+        <v>210</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B234" t="s">
-        <v>250</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>232</v>
+      </c>
+      <c r="B235" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>246</v>
+      </c>
+      <c r="B236" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>229</v>
+      </c>
+      <c r="B237" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>232</v>
+      </c>
+      <c r="B238" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>243</v>
+      </c>
+      <c r="B239" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>251</v>
+      </c>
+      <c r="B240" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>293</v>
+      </c>
+      <c r="B241" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>234</v>
+      </c>
+      <c r="B242" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>302</v>
+      </c>
+      <c r="B243" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>230</v>
+      </c>
+      <c r="B244" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>278</v>
+      </c>
+      <c r="B245" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>232</v>
+      </c>
+      <c r="B246" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>236</v>
+      </c>
+      <c r="B247" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>270</v>
+      </c>
+      <c r="B248" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>229</v>
+      </c>
+      <c r="B249" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>278</v>
+      </c>
+      <c r="B250" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>285</v>
+      </c>
+      <c r="B251" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>202</v>
+      </c>
+      <c r="B252" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>233</v>
+      </c>
+      <c r="B253" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>284</v>
+      </c>
+      <c r="B254" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>320</v>
+      </c>
+      <c r="B255" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>232</v>
+      </c>
+      <c r="B256" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>321</v>
+      </c>
+      <c r="B257" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>280</v>
+      </c>
+      <c r="B258" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>322</v>
+      </c>
+      <c r="B259" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>235</v>
+      </c>
+      <c r="B260" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_supercategory.xlsx
+++ b/Avantis Mapping/SPARQL_supercategory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44039686-1D5A-4AFC-B78E-8B922B2F1C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F82979-E0EB-4C1E-A352-F16F8B8C1E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="326">
   <si>
     <t>Vessel,Pressure,Surge</t>
   </si>
@@ -725,255 +725,69 @@
     <t>Control Panel,Fire</t>
   </si>
   <si>
-    <t>fixed gas detector</t>
-  </si>
-  <si>
-    <t>transformer</t>
-  </si>
-  <si>
-    <t>actuator</t>
-  </si>
-  <si>
-    <t>valve</t>
-  </si>
-  <si>
-    <t>instrument transmitter</t>
-  </si>
-  <si>
-    <t>mixer or agitator</t>
-  </si>
-  <si>
-    <t>motor</t>
-  </si>
-  <si>
-    <t>hoist</t>
-  </si>
-  <si>
-    <t>compressor</t>
-  </si>
-  <si>
-    <t>well</t>
-  </si>
-  <si>
     <t>Well,Reservoir</t>
   </si>
   <si>
-    <t>computer</t>
-  </si>
-  <si>
-    <t>dryer</t>
-  </si>
-  <si>
-    <t>lighting unit</t>
-  </si>
-  <si>
-    <t>crane</t>
-  </si>
-  <si>
     <t>Crane,Overhead,Fixed</t>
   </si>
   <si>
-    <t>battery charger</t>
-  </si>
-  <si>
-    <t>instrument gauge or display</t>
-  </si>
-  <si>
     <t>Crane,Overhead</t>
   </si>
   <si>
-    <t>hot work equipment</t>
-  </si>
-  <si>
-    <t>temperature switch</t>
-  </si>
-  <si>
     <t>Switch,Temperature-Low</t>
   </si>
   <si>
-    <t>clarifier</t>
-  </si>
-  <si>
-    <t>grinder or comminutor</t>
-  </si>
-  <si>
-    <t>passenger vehicle</t>
-  </si>
-  <si>
-    <t>roof</t>
-  </si>
-  <si>
-    <t>UV disinfection assembly</t>
-  </si>
-  <si>
-    <t>PLC</t>
-  </si>
-  <si>
-    <t>air handler unit</t>
-  </si>
-  <si>
-    <t>stationary tool</t>
-  </si>
-  <si>
-    <t>forklift</t>
-  </si>
-  <si>
-    <t>chemical or concentration sensor element</t>
-  </si>
-  <si>
     <t>Sensor,Gas</t>
   </si>
   <si>
-    <t>heater</t>
-  </si>
-  <si>
     <t>Crane,Overhead,Travelling</t>
   </si>
   <si>
-    <t>generator</t>
-  </si>
-  <si>
-    <t>speed switch</t>
-  </si>
-  <si>
-    <t>battery</t>
-  </si>
-  <si>
-    <t>chemical storage tank</t>
-  </si>
-  <si>
-    <t>server appliance</t>
-  </si>
-  <si>
-    <t>process control panel</t>
-  </si>
-  <si>
-    <t>blower</t>
-  </si>
-  <si>
-    <t>position switch</t>
-  </si>
-  <si>
     <t>Switch,Position-High</t>
   </si>
   <si>
-    <t>incinerator</t>
-  </si>
-  <si>
-    <t>level transmitter</t>
-  </si>
-  <si>
     <t>Crane,Travelling</t>
   </si>
   <si>
-    <t>cable segment</t>
-  </si>
-  <si>
     <t>Cable,Busduct</t>
   </si>
   <si>
-    <t>air damper</t>
-  </si>
-  <si>
-    <t>pressure vessel</t>
-  </si>
-  <si>
-    <t>centrifuge</t>
-  </si>
-  <si>
-    <t>flow switch</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>flocculation tank</t>
-  </si>
-  <si>
-    <t>screen</t>
-  </si>
-  <si>
-    <t>portable gas detector</t>
-  </si>
-  <si>
     <t>Switch,Position-Low</t>
   </si>
   <si>
-    <t>pressure switch</t>
-  </si>
-  <si>
     <t>Switch,Pressure-Low</t>
   </si>
   <si>
-    <t>load break disconnect switch</t>
-  </si>
-  <si>
     <t>fvyuLoad Break Switch</t>
   </si>
   <si>
-    <t>MV electrical cabinet</t>
-  </si>
-  <si>
     <t>Switch,Pressure-High</t>
   </si>
   <si>
-    <t>level switch</t>
-  </si>
-  <si>
     <t>Switch,Level-Low</t>
   </si>
   <si>
-    <t>elevator</t>
-  </si>
-  <si>
-    <t>strainer</t>
-  </si>
-  <si>
     <t>Switch,Level-Low-Low</t>
   </si>
   <si>
     <t>Switch,Temperature-High</t>
   </si>
   <si>
-    <t>compactor</t>
-  </si>
-  <si>
     <t>Compactor,Mobile</t>
   </si>
   <si>
     <t>Compactor,Stationary,Paper</t>
   </si>
   <si>
-    <t>weight scale</t>
-  </si>
-  <si>
-    <t>LV electrical panel</t>
-  </si>
-  <si>
-    <t>pressure transmitter</t>
-  </si>
-  <si>
     <t>Switch,Level-High-High</t>
   </si>
   <si>
-    <t>storage tank</t>
-  </si>
-  <si>
-    <t>vibration sensor element</t>
-  </si>
-  <si>
     <t>Switch,Vibration-High</t>
   </si>
   <si>
-    <t>pond</t>
-  </si>
-  <si>
     <t>Lagoon</t>
   </si>
   <si>
-    <t>waste gas burner</t>
-  </si>
-  <si>
     <t>Switch,Vibration-Low</t>
   </si>
   <si>
@@ -986,28 +800,217 @@
     <t>Cable,Teck</t>
   </si>
   <si>
-    <t>screw conveyor</t>
-  </si>
-  <si>
-    <t>air scrubber</t>
-  </si>
-  <si>
     <t>Crane,Overhead,Fixed,Paper</t>
   </si>
   <si>
     <t>Switch,Level-High</t>
   </si>
   <si>
-    <t>conveyor</t>
-  </si>
-  <si>
-    <t>chemical or concentration analyzer</t>
-  </si>
-  <si>
-    <t>air duct segment</t>
-  </si>
-  <si>
     <t>Silencer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00531</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00144</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00200</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00208</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00781</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00245</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00447</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00665</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00121</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00583</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00359</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00142</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00179</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00422</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00526</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00806</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00755</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00466</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00219</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00251</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00445</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00138</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00372</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00306</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00667</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00148</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00126</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00234</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00192</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00232</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00699</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00110</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00792</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00405</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00795</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00428</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00478</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00233</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00580</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00367</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00613</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00650</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00708</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00467</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00605</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00167</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00364</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00119</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00147</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00418</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00734</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00710</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00604</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00680</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00111</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00487</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00590</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00124</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00606</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00435</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00397</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00211</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00209</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00703</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00291</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00559</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00168</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00811</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -1015,11 +1018,10 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis) 
+SELECT (STR(?sub) AS ?TWONTO) (STR(?object) AS ?Avantis)
 WHERE { 
-    ?TWONTO tw:is_superclass_of_Avantis_category ?object .
-    ?TWONTO rdfs:label ?TWONTO_Label .
-    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
+    ?sub tw:is_superclass_of_Avantis_category ?object .
+    FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
   </si>
 </sst>
@@ -1027,7 +1029,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1046,6 +1048,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1080,21 +1090,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -1450,9 +1462,9 @@
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="203" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>324</v>
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1464,1307 +1476,1307 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>48</v>
+      <c r="A3" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="B14" t="s">
-        <v>239</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="B21" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s">
-        <v>197</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>231</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s">
-        <v>247</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s">
-        <v>250</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>231</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>229</v>
+        <v>287</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="B50" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="B51" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B52" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="B54" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B56" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="B60" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="B61" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>232</v>
+        <v>294</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="B63" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="B65" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="B69" t="s">
-        <v>215</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="B70" t="s">
-        <v>209</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>232</v>
+        <v>299</v>
       </c>
       <c r="B74" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B77" t="s">
-        <v>272</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>247</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B84" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B85" t="s">
-        <v>195</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="B86" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B87" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="B88" t="s">
-        <v>275</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B89" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B90" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>235</v>
+        <v>302</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>248</v>
+        <v>303</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="B93" t="s">
-        <v>0</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B94" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="B95" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="B96" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="B97" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B98" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="B99" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="B100" t="s">
-        <v>38</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>161</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="B102" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="B104" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="B105" t="s">
-        <v>54</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>245</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>232</v>
+        <v>307</v>
       </c>
       <c r="B107" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="B108" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B109" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B111" t="s">
-        <v>67</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="B113" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="B114" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="B115" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="B116" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="B117" t="s">
-        <v>221</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="B118" t="s">
-        <v>286</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B119" t="s">
-        <v>288</v>
+        <v>171</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="B120" t="s">
-        <v>290</v>
+        <v>183</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B122" t="s">
-        <v>226</v>
+        <v>91</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B123" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="B124" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="B125" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B126" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="B127" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B128" t="s">
-        <v>292</v>
+        <v>78</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="B129" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="B131" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>229</v>
+        <v>300</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>237</v>
+        <v>309</v>
       </c>
       <c r="B135" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="B136" t="s">
-        <v>294</v>
+        <v>153</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="B139" t="s">
-        <v>181</v>
+        <v>100</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>259</v>
+        <v>310</v>
       </c>
       <c r="B140" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B141" t="s">
-        <v>91</v>
+        <v>226</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="B142" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>232</v>
+        <v>309</v>
       </c>
       <c r="B143" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>234</v>
+        <v>312</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="B145" t="s">
-        <v>112</v>
+        <v>238</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="B146" t="s">
-        <v>8</v>
+        <v>221</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="B147" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="B148" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="B150" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="B151" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="B152" t="s">
-        <v>297</v>
+        <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>232</v>
+        <v>303</v>
       </c>
       <c r="B153" t="s">
-        <v>172</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B154" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B155" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B156" t="s">
-        <v>298</v>
+        <v>166</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B157" t="s">
-        <v>300</v>
+        <v>117</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="B158" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B159" t="s">
-        <v>301</v>
+        <v>52</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="B160" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="B161" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B163" t="s">
-        <v>223</v>
+        <v>38</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="B164" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="B165" t="s">
-        <v>168</v>
+        <v>63</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -2772,765 +2784,768 @@
         <v>278</v>
       </c>
       <c r="B166" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="B167" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="B168" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
       <c r="B169" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="B170" t="s">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B171" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B172" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="B173" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="B174" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>236</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="B176" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="B177" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="B178" t="s">
-        <v>113</v>
+        <v>195</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>232</v>
+        <v>300</v>
       </c>
       <c r="B179" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="B180" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B181" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="B182" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="B183" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B184" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>233</v>
+        <v>313</v>
       </c>
       <c r="B186" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B187" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="B188" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="B189" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
       <c r="B190" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="B191" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
       <c r="B192" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>240</v>
+        <v>317</v>
       </c>
       <c r="B193" t="s">
-        <v>82</v>
+        <v>209</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="B194" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="B195" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>232</v>
+        <v>318</v>
       </c>
       <c r="B196" t="s">
-        <v>103</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="B197" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="B198" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>232</v>
+        <v>304</v>
       </c>
       <c r="B199" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="B200" t="s">
-        <v>308</v>
+        <v>213</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B201" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="B202" t="s">
-        <v>56</v>
+        <v>201</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B203" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
       <c r="B204" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="B205" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="B206" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="B207" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="B208" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B209" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="B210" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B211" t="s">
-        <v>208</v>
+        <v>25</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="B212" t="s">
-        <v>222</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="B213" t="s">
-        <v>1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="B214" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>278</v>
+        <v>321</v>
       </c>
       <c r="B215" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="B216" t="s">
-        <v>312</v>
+        <v>29</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="B217" t="s">
-        <v>313</v>
+        <v>32</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B218" t="s">
-        <v>225</v>
+        <v>145</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B219" t="s">
-        <v>203</v>
+        <v>50</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="B220" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B221" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="B222" t="s">
-        <v>315</v>
+        <v>74</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="B223" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B224" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="B225" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="B226" t="s">
-        <v>191</v>
+        <v>69</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="B227" t="s">
-        <v>4</v>
+        <v>95</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>317</v>
+        <v>278</v>
       </c>
       <c r="B228" t="s">
-        <v>6</v>
+        <v>119</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="B229" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B230" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>230</v>
+        <v>278</v>
       </c>
       <c r="B231" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="B232" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="B233" t="s">
-        <v>77</v>
+        <v>211</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>231</v>
+        <v>307</v>
       </c>
       <c r="B234" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="B235" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="B236" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="B237" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>232</v>
+        <v>323</v>
       </c>
       <c r="B238" t="s">
-        <v>65</v>
+        <v>197</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="B239" t="s">
-        <v>318</v>
+        <v>230</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B240" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B241" t="s">
-        <v>319</v>
+        <v>118</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>18</v>
+        <v>186</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="B243" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="B244" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B245" t="s">
-        <v>144</v>
+        <v>24</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>232</v>
+        <v>321</v>
       </c>
       <c r="B246" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="B247" t="s">
-        <v>212</v>
+        <v>93</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B248" t="s">
-        <v>205</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
+        <v>324</v>
+      </c>
+      <c r="B249" t="s">
         <v>229</v>
-      </c>
-      <c r="B249" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="B250" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B251" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>202</v>
+        <v>99</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="B253" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="B254" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>320</v>
+        <v>263</v>
       </c>
       <c r="B255" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="B256" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="B257" t="s">
-        <v>224</v>
+        <v>133</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B258" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="B259" t="s">
-        <v>323</v>
+        <v>159</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="B260" t="s">
-        <v>147</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" location="00531" xr:uid="{191A8FB9-86B0-4404-9C5E-6A4CE4EB29BA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Avantis Mapping/SPARQL_supercategory.xlsx
+++ b/Avantis Mapping/SPARQL_supercategory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F82979-E0EB-4C1E-A352-F16F8B8C1E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACD289D-04D9-41C5-A193-FC0999118DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -3540,12 +3540,9 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" location="00531" xr:uid="{191A8FB9-86B0-4404-9C5E-6A4CE4EB29BA}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>